--- a/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="58">
   <si>
     <t>Result</t>
   </si>
@@ -183,6 +183,33 @@
   </si>
   <si>
     <t>Sat Oct 04 16:23:50 EDT 2025</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:57:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:57:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:58:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:17:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:18:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:19:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 17:47:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 17:47:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri May 22 17:47:39 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -586,10 +613,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -603,10 +630,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -620,10 +647,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>

--- a/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
+++ b/KatalonData/RADTestData/JointFilerSSNmoreThan9Error.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="64">
   <si>
     <t>Result</t>
   </si>
@@ -210,6 +210,24 @@
   </si>
   <si>
     <t>Fri May 22 17:47:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:01:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:02:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:02:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:59:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:59:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:00:00 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -583,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C1F8A3-6DEF-49A6-954D-D8228E68B4AC}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
@@ -612,11 +630,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>55</v>
+      <c r="B2" t="s" s="1">
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -629,11 +647,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>56</v>
+      <c r="B3" t="s" s="1">
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -646,11 +664,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>57</v>
+      <c r="B4" t="s" s="1">
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
